--- a/BokCustomer/wwwroot/templates/CSCE/Raccolta-dati-rischio-chimico.xlsx
+++ b/BokCustomer/wwwroot/templates/CSCE/Raccolta-dati-rischio-chimico.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr filterPrivacy="1" codeName="Questa_cartella_di_lavoro" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{288287FD-9BDA-A346-B651-BFDBDAFBB0E2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B0FB275-55CB-7440-BAEB-DAA1C8DD2492}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17100" yWindow="600" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11920" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ELENCO PRODOTTI" sheetId="2" r:id="rId1"/>
@@ -28,18 +28,7 @@
     <definedName name="IDOrganization">'ELENCO PRODOTTI'!$C$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'ELENCO PRODOTTI'!$7:$7</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -68,12 +57,21 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Inserire le mansioni che
-utilizzano il prodotto
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">utilizzano il prodotto
 </t>
         </r>
       </text>
@@ -494,9 +492,6 @@
     <t>Aspirazione localizzata</t>
   </si>
   <si>
-    <t>Bassa volatilità</t>
-  </si>
-  <si>
     <t>1 - 10 kg</t>
   </si>
   <si>
@@ -504,9 +499,6 @@
   </si>
   <si>
     <t>Segregazione/separazione</t>
-  </si>
-  <si>
-    <t>Media/Alta volatilità e polveri fini</t>
   </si>
   <si>
     <t>10 - 100 kg</t>
@@ -532,12 +524,18 @@
   <si>
     <t>Release 1.0 del 05/03/26</t>
   </si>
+  <si>
+    <t>Liquidi Media/Alta volatilità e polveri fini</t>
+  </si>
+  <si>
+    <t>Liquidi a Bassa volatilità</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -645,6 +643,18 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="20"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1044,9 +1054,6 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1085,6 +1092,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2206,7 +2216,7 @@
       <c r="N1" s="46"/>
       <c r="O1" s="46"/>
       <c r="P1" s="32" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:16" s="31" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -2214,22 +2224,22 @@
         <v>34</v>
       </c>
       <c r="B3" s="35"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="60"/>
     </row>
     <row r="4" spans="1:16" s="31" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="35" t="s">
         <v>35</v>
       </c>
       <c r="B4" s="35"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
       <c r="E4" s="12"/>
       <c r="F4" s="12"/>
       <c r="G4" s="12"/>
@@ -2313,7 +2323,7 @@
         <v>72</v>
       </c>
       <c r="G9" s="42" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H9" s="42" t="s">
         <v>73</v>
@@ -12460,12 +12470,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="37" x14ac:dyDescent="0.45">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
     </row>
     <row r="5" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="20" t="s">
@@ -13045,28 +13055,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="37" x14ac:dyDescent="0.45">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
+      <c r="S1" s="48"/>
+      <c r="T1" s="48"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B5" s="21" t="s">
@@ -13088,7 +13098,7 @@
         <v>58</v>
       </c>
       <c r="T5" s="21" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.2">
@@ -13134,15 +13144,15 @@
         <v>91</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>94</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>49</v>
@@ -13154,18 +13164,18 @@
         <v>84</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>50</v>
@@ -13177,10 +13187,10 @@
         <v>85</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.2">
@@ -13188,7 +13198,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>51</v>
@@ -13221,11 +13231,11 @@
   <sheetData>
     <row r="1" spans="2:4" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:4" s="29" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="58"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="57"/>
     </row>
     <row r="3" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="15"/>
@@ -13233,10 +13243,10 @@
       <c r="D3" s="18"/>
     </row>
     <row r="4" spans="2:4" ht="64" x14ac:dyDescent="0.2">
-      <c r="B4" s="59" t="s">
+      <c r="B4" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="60"/>
+      <c r="C4" s="59"/>
       <c r="D4" s="17" t="s">
         <v>16</v>
       </c>
@@ -13247,10 +13257,10 @@
       <c r="D5" s="18"/>
     </row>
     <row r="6" spans="2:4" ht="48" x14ac:dyDescent="0.2">
-      <c r="B6" s="52" t="s">
+      <c r="B6" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="53"/>
+      <c r="C6" s="52"/>
       <c r="D6" s="17" t="s">
         <v>18</v>
       </c>
@@ -13261,10 +13271,10 @@
       <c r="D7" s="18"/>
     </row>
     <row r="8" spans="2:4" ht="48" x14ac:dyDescent="0.2">
-      <c r="B8" s="52" t="s">
+      <c r="B8" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="53"/>
+      <c r="C8" s="52"/>
       <c r="D8" s="17" t="s">
         <v>20</v>
       </c>
@@ -13275,63 +13285,63 @@
       <c r="D9" s="18"/>
     </row>
     <row r="10" spans="2:4" ht="65" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="54" t="s">
+      <c r="B10" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="55"/>
+      <c r="C10" s="54"/>
       <c r="D10" s="19" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="11" spans="2:4" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="2:4" ht="21" x14ac:dyDescent="0.25">
-      <c r="B12" s="56" t="s">
+      <c r="B12" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="57"/>
-      <c r="D12" s="58"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="57"/>
     </row>
     <row r="13" spans="2:4" ht="32" x14ac:dyDescent="0.2">
-      <c r="B13" s="50" t="s">
+      <c r="B13" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="51"/>
+      <c r="C13" s="50"/>
       <c r="D13" s="17" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="52" t="s">
+      <c r="B14" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="53"/>
+      <c r="C14" s="52"/>
       <c r="D14" s="17" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="15" spans="2:4" ht="80" x14ac:dyDescent="0.2">
-      <c r="B15" s="50" t="s">
+      <c r="B15" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="51"/>
+      <c r="C15" s="50"/>
       <c r="D15" s="17" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" spans="2:4" ht="48" x14ac:dyDescent="0.2">
-      <c r="B16" s="50" t="s">
+      <c r="B16" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="51"/>
+      <c r="C16" s="50"/>
       <c r="D16" s="17" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="49" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="54" t="s">
+      <c r="B17" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="55"/>
+      <c r="C17" s="54"/>
       <c r="D17" s="19" t="s">
         <v>33</v>
       </c>
